--- a/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
@@ -539,10 +539,10 @@
         <v>0.23</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.37</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13">
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.48</v>
+        <v>6.86</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>5.53</v>
+        <v>6.93</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bases, contrapisos y nivelación</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-01-050.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Subcapítulo: Bases, contrapisos y nivelación</t>
+          <t>Subcapítulo: Bases, afirmados y nivelación</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preparación de losa o piso existente que permanece como base, mediante limpieza, saneado y aplicación de puente de adherencia, para recibir una capa de recrecido o un piso adherido. Se emplea en reforma cuando no se demuele la base y hay que garantizar que la capa nueva no se despegue. Incluye el sondeo por golpeo y el saneado de las zonas huecas, el desengrasado y eliminación de restos de adhesivos o pinturas, el aspirado del polvo, la apertura del poro mediante lijado o repicado ligero y la aplicación del puente de adherencia respetando el tiempo abierto antes de recibir la capa siguiente. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
+          <t xml:space="preserve">Preparación de losa o piso existente que permanece como base, mediante limpieza, saneado y aplicación de puente de adherencia, para recibir una capa de afirmado o un piso adherido. Se emplea en reforma cuando no se demuele la base y hay que garantizar que la capa nueva no se despegue. Incluye el sondeo por golpeo y el saneado de las zonas huecas, el desengrasado y eliminación de restos de adhesivos o pinturas, el aspirado del polvo, la apertura del poro mediante lijado o repicado ligero y la aplicación del puente de adherencia respetando el tiempo abierto antes de recibir la capa siguiente. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
 </t>
         </is>
       </c>
